--- a/target/classes/com/mycompany/ocxrst/BASES/PAGOS.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/PAGOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03ED2A7C-6B61-4537-9C0F-60A8FCC6AE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F398AFBE-9B63-46F1-91A3-D3F5B9142F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3670" yWindow="2630" windowWidth="14400" windowHeight="8170" xr2:uid="{547646D9-8744-43CC-ADA2-856FFD60DD7E}"/>
+    <workbookView xWindow="3120" yWindow="1200" windowWidth="14400" windowHeight="8170" xr2:uid="{547646D9-8744-43CC-ADA2-856FFD60DD7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>PAGOS</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Otros</t>
+  </si>
+  <si>
+    <t>** Selecciona una opción **</t>
   </si>
 </sst>
 </file>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCC866F-3AA3-41EC-B2BA-199ABD3D5D6B}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -429,16 +432,21 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
